--- a/DateBase/orders/Nha Thu_2026-6-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-15.xlsx
@@ -768,6 +768,9 @@
         <v xml:space="preserve">416_翠珠紫_Didiscus caeruleus
 blue_Trachymene Coerulea_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -826,7 +829,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01051055531055103030101015105755136111055515101010510133055100</v>
+        <v>010510555310551030301010151057551361110555151010105101330551010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -772,9 +772,178 @@
         <v>10</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>5</v>
+      </c>
+      <c r="C42" t="str">
+        <v>780_贝壳草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>586_洋牡丹白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>590_洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>792_珍珠梅白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>790_铁线莲粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>6</v>
+      </c>
+      <c r="C49" t="str">
+        <v>533_风车果_scabiosa pods_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>1</v>
+      </c>
+      <c r="C50" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F51" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2</v>
+      </c>
+      <c r="C56" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F59" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F60" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -829,7 +998,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010510555310551030301010151057551361110555151010105101330551010</v>
+        <v>010510555310551030301010151057551361110555151010105101330551010610105531010391275613710750</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L66"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -940,10 +940,59 @@
       <c r="A61" t="str">
         <v>3</v>
       </c>
+      <c r="C61" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F61" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F62" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F63" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F64" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>4</v>
+      </c>
+      <c r="C65" t="str">
+        <v>102_绣球重瓣白_Hydrangea White D_Hydrangea L._1stem</v>
+      </c>
+      <c r="F65" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>790_铁线莲粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L66"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -998,7 +1047,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010510555310551030301010151057551361110555151010105101330551010610105531010391275613710750</v>
+        <v>01051055531055103030101015105755136111055515101010510133055101061010553101039127561371075148510303</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-15.xlsx
@@ -1049,6 +1049,9 @@
       <c r="G2" t="str">
         <v>01051055531055103030101015105755136111055515101010510133055101061010553101039127561371075148510303</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
